--- a/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
+++ b/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
@@ -1821,34 +1821,34 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>8431000</v>
+        <v>7419000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>34553</v>
+        <v>30406</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>7419280</v>
+        <v>7419000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>30407</v>
+        <v>30406</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6349,12 +6349,12 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 244呎 (开放式)
-$843万
-$34,553/呎
-(在售)</t>
+$742万
+$30,406/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>

--- a/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
+++ b/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -6354,7 +6354,7 @@
           <t>D | 244呎 (开放式)
 $742万
 $30,406/呎
-(26年-09月-22日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>

--- a/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
+++ b/港岛-半山区西部-Upper Central/Upper Central_销控明细表.xlsx
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>8560000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>35082</v>
+        <v>35372</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>7532800</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>30872</v>
+        <v>31127</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>8486000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>35066</v>
+        <v>35358</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>7467680</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>30858</v>
+        <v>31115</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>5193000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>33288</v>
+        <v>33503</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>4569840</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>29294</v>
+        <v>29483</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>6008000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>33944</v>
+        <v>34331</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>5287040</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>29870</v>
+        <v>30212</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>12566000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>32303</v>
+        <v>32387</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>12566000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>32303</v>
+        <v>32387</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>9114000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>37352</v>
+        <v>37661</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>8020320</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>32870</v>
+        <v>33142</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>7281000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>36959</v>
+        <v>37338</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>6407280</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>32524</v>
+        <v>32858</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>11809000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30357</v>
+        <v>30436</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>11809000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>30357</v>
+        <v>30436</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>6984000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>28623</v>
+        <v>28860</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>6984000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>28623</v>
+        <v>28860</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>11704000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>30087</v>
+        <v>30165</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>11704000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>30087</v>
+        <v>30165</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>6921000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>28365</v>
+        <v>28599</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>6921000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>28365</v>
+        <v>28599</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>6264000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>31797</v>
+        <v>32123</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>6264000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>31797</v>
+        <v>32123</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>7419000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>30406</v>
+        <v>30657</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>7419000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>30406</v>
+        <v>30657</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>6775000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>28112</v>
+        <v>28347</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>6775000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>28112</v>
+        <v>28347</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>4704000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>28000</v>
+        <v>28168</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>4704000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>28000</v>
+        <v>28168</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>5887000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>30036</v>
+        <v>30345</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>5887000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30036</v>
+        <v>30345</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>6890000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>28238</v>
+        <v>28471</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>6890000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>28238</v>
+        <v>28471</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>6606000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>27411</v>
+        <v>27640</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>6606000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>27411</v>
+        <v>27640</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>4359000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>25946</v>
+        <v>26102</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>4359000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>25946</v>
+        <v>26102</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>5628000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>28714</v>
+        <v>29010</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>5628000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>28714</v>
+        <v>29010</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>6624000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>27148</v>
+        <v>27372</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>6624000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>27148</v>
+        <v>27372</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>6739000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>27963</v>
+        <v>28197</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>6739000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>27963</v>
+        <v>28197</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>4316000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>25690</v>
+        <v>25844</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>4316000</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>25690</v>
+        <v>25844</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>5154000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>26296</v>
+        <v>26567</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>5154000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>26296</v>
+        <v>26567</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>6249000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>25611</v>
+        <v>25822</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>6249000</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>25611</v>
+        <v>25822</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>6171000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>25606</v>
+        <v>25820</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>6171000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>25606</v>
+        <v>25820</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>4623000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>27518</v>
+        <v>27683</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>4623000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>27518</v>
+        <v>27683</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>5360000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>27347</v>
+        <v>27629</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>5360000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>27347</v>
+        <v>27629</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>6437000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>26381</v>
+        <v>26599</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>6437000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>26381</v>
+        <v>26599</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>6113000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>25365</v>
+        <v>25577</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>6113000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>25365</v>
+        <v>25577</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>4232000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>25190</v>
+        <v>25341</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>4232000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>25190</v>
+        <v>25341</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>5158000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>26316</v>
+        <v>26588</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>5158000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>26316</v>
+        <v>26588</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>6375000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>26127</v>
+        <v>26343</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>6375000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>26127</v>
+        <v>26343</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>6054000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>25120</v>
+        <v>25331</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>6054000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>25120</v>
+        <v>25331</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>4401000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>26196</v>
+        <v>26353</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>4401000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>26196</v>
+        <v>26353</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>5009000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>25556</v>
+        <v>25820</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>5009000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>25556</v>
+        <v>25820</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>6347000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>26012</v>
+        <v>26227</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>6347000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>26012</v>
+        <v>26227</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>6267000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>26004</v>
+        <v>26222</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>6267000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>26004</v>
+        <v>26222</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>4170000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>24821</v>
+        <v>24970</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>4170000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>24821</v>
+        <v>24970</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>5085000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>25944</v>
+        <v>26211</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>5085000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>25944</v>
+        <v>26211</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>6014000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>24648</v>
+        <v>24851</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>6014000</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>24648</v>
+        <v>24851</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>6177000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>25631</v>
+        <v>25845</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>6177000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>25631</v>
+        <v>25845</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>4442000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>26440</v>
+        <v>26599</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>4442000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>26440</v>
+        <v>26599</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>5011000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>25566</v>
+        <v>25830</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>5011000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>25566</v>
+        <v>25830</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>5956000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>24410</v>
+        <v>24612</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>5956000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>24410</v>
+        <v>24612</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>5882000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>24407</v>
+        <v>24611</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>5882000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>24407</v>
+        <v>24611</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>4068000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>24214</v>
+        <v>24359</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>4068000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>24214</v>
+        <v>24359</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>4866000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>24827</v>
+        <v>25082</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>4866000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>24827</v>
+        <v>25082</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>5899000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>24176</v>
+        <v>24376</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>5899000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>24176</v>
+        <v>24376</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>6060000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>25145</v>
+        <v>25356</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>6060000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>25145</v>
+        <v>25356</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>4355000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>25923</v>
+        <v>26078</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>4355000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>25923</v>
+        <v>26078</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>4915000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>25077</v>
+        <v>25335</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>4915000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>25077</v>
+        <v>25335</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>5959000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>24422</v>
+        <v>24624</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>5959000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>24422</v>
+        <v>24624</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>6002000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>24905</v>
+        <v>25113</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>6002000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>24905</v>
+        <v>25113</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>3988000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>23738</v>
+        <v>23880</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>3988000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>23738</v>
+        <v>23880</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>5065000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>25842</v>
+        <v>26108</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>5065000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>25842</v>
+        <v>26108</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>6017000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>24660</v>
+        <v>24864</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>6017000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>24660</v>
+        <v>24864</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>5943000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>24660</v>
+        <v>24866</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>5943000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>24660</v>
+        <v>24866</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>4269000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>25411</v>
+        <v>25563</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>4269000</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>25411</v>
+        <v>25563</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>5011000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>25566</v>
+        <v>25830</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>5011000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>25566</v>
+        <v>25830</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>5730000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>23484</v>
+        <v>23678</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>5730000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>23484</v>
+        <v>23678</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>5659000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>23481</v>
+        <v>23678</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>5659000</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>23481</v>
+        <v>23678</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>4104000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>24429</v>
+        <v>24575</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>4104000</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>24429</v>
+        <v>24575</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>4775000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>24362</v>
+        <v>24613</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>4775000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>24362</v>
+        <v>24613</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>5789000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>23725</v>
+        <v>23921</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>5789000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>23725</v>
+        <v>23921</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>5605000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>23257</v>
+        <v>23452</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>5605000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>23257</v>
+        <v>23452</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>4186000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>24917</v>
+        <v>25066</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>4186000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>24917</v>
+        <v>25066</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>4636000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>23653</v>
+        <v>23897</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>4636000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>23653</v>
+        <v>23897</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>5648000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>23148</v>
+        <v>23339</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>5648000</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>23148</v>
+        <v>23339</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>5803000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>24079</v>
+        <v>24280</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>5803000</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>24079</v>
+        <v>24280</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>4044000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>24071</v>
+        <v>24216</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>4044000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>24071</v>
+        <v>24216</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>4614000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>23541</v>
+        <v>23784</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>4614000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>23541</v>
+        <v>23784</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>5567000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>22816</v>
+        <v>23004</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>5567000</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>22816</v>
+        <v>23004</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>5720000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>23734</v>
+        <v>23933</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>5720000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>23734</v>
+        <v>23933</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>4104000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>24429</v>
+        <v>24575</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>4104000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>24429</v>
+        <v>24575</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>4729000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>24128</v>
+        <v>24376</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>4729000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>24128</v>
+        <v>24376</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>5475000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>26196</v>
+        <v>26322</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>5475000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>26196</v>
+        <v>26322</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>4063000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>24185</v>
+        <v>24329</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>4063000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>24185</v>
+        <v>24329</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>4504000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>22980</v>
+        <v>23216</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>4504000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>22980</v>
+        <v>23216</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6148,33 +6148,33 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 177呎 (开放式)
+          <t>A | 175呎 (开放式)
 $601万
-$33,944/呎
+$34,331/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 156呎 (开放式)
+          <t>B | 155呎 (开放式)
 $519万
-$33,288/呎
+$33,503/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 242呎 (开放式)
+          <t>C | 240呎 (开放式)
 $849万
-$35,066/呎
+$35,358/呎
 (已定价未售)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $856万
-$35,082/呎
+$35,372/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -6228,9 +6228,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 197呎 (开放式)
+          <t>A | 195呎 (开放式)
 $728万
-$36,959/呎
+$37,338/呎
 (在售)</t>
         </is>
       </c>
@@ -6238,17 +6238,17 @@
       <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $911万
-$37,352/呎
+$37,661/呎
 (在售)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>E | 389呎 (2房)
+          <t>E | 388呎 (2房)
 $1257万
-$32,303/呎
+$32,387/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -6271,17 +6271,17 @@
       <c r="D8" s="21" t="inlineStr"/>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $698万
-$28,623/呎
+$28,860/呎
 (25年-12月-15日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>E | 389呎 (2房)
+          <t>E | 388呎 (2房)
 $1181万
-$30,357/呎
+$30,436/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -6294,9 +6294,9 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>A | 197呎 (开放式)
+          <t>A | 195呎 (开放式)
 $626万
-$31,797/呎
+$32,123/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -6304,17 +6304,17 @@
       <c r="D9" s="21" t="inlineStr"/>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $692万
-$28,365/呎
+$28,599/呎
 (26年-03月-25日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>E | 389呎 (2房)
+          <t>E | 388呎 (2房)
 $1170万
-$30,087/呎
+$30,165/呎
 (26年-02月-03日)</t>
         </is>
       </c>
@@ -6327,33 +6327,33 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $589万
-$30,036/呎
+$30,345/呎
 (26年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $470万
-$28,000/呎
+$28,168/呎
 (25年-05月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $678万
-$28,112/呎
+$28,347/呎
 (25年-12月-22日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $742万
-$30,406/呎
+$30,657/呎
 (26年-10月-08日)</t>
         </is>
       </c>
@@ -6367,33 +6367,33 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $563万
-$28,714/呎
+$29,010/呎
 (26年-05月-28日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $436万
-$25,946/呎
+$26,102/呎
 (25年-03月-28日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $661万
-$27,411/呎
+$27,640/呎
 (26年-05月-11日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $689万
-$28,238/呎
+$28,471/呎
 (26年-07月-15日)</t>
         </is>
       </c>
@@ -6407,33 +6407,33 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $515万
-$26,296/呎
+$26,567/呎
 (25年-12月-12日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $432万
-$25,690/呎
+$25,844/呎
 (25年-03月-04日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $674万
-$27,963/呎
+$28,197/呎
 (26年-07月-16日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $662万
-$27,148/呎
+$27,372/呎
 (26年-05月-20日)</t>
         </is>
       </c>
@@ -6447,33 +6447,33 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $536万
-$27,347/呎
+$27,629/呎
 (26年-05月-20日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $462万
-$27,518/呎
+$27,683/呎
 (26年-02月-13日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $617万
-$25,606/呎
+$25,820/呎
 (25年-12月-09日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $625万
-$25,611/呎
+$25,822/呎
 (25年-01月-14日)</t>
         </is>
       </c>
@@ -6487,33 +6487,33 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $516万
-$26,316/呎
+$26,588/呎
 (26年-01月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $423万
-$25,190/呎
+$25,341/呎
 (25年-02月-21日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $611万
-$25,365/呎
+$25,577/呎
 (25年-12月-04日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $644万
-$26,381/呎
+$26,599/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -6527,33 +6527,33 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $501万
-$25,556/呎
+$25,820/呎
 (25年-11月-27日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $440万
-$26,196/呎
+$26,353/呎
 (25年-12月-18日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $605万
-$25,120/呎
+$25,331/呎
 (25年-12月-02日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $638万
-$26,127/呎
+$26,343/呎
 (26年-03月-27日)</t>
         </is>
       </c>
@@ -6567,33 +6567,33 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $508万
-$25,944/呎
+$26,211/呎
 (26年-01月-21日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $417万
-$24,821/呎
+$24,970/呎
 (24年-11月-05日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $627万
-$26,004/呎
+$26,222/呎
 (26年-05月-29日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $635万
-$26,012/呎
+$26,227/呎
 (26年-02月-13日)</t>
         </is>
       </c>
@@ -6607,33 +6607,33 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $501万
-$25,566/呎
+$25,830/呎
 (26年-01月-06日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $444万
-$26,440/呎
+$26,599/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $618万
-$25,631/呎
+$25,845/呎
 (26年-04月-24日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $601万
-$24,648/呎
+$24,851/呎
 (26年-01月-27日)</t>
         </is>
       </c>
@@ -6647,33 +6647,33 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $487万
-$24,827/呎
+$25,082/呎
 (25年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $407万
-$24,214/呎
+$24,359/呎
 (24年-10月-28日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $588万
-$24,407/呎
+$24,611/呎
 (26年-01月-27日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $596万
-$24,410/呎
+$24,612/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -6687,33 +6687,33 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $492万
-$25,077/呎
+$25,335/呎
 (25年-12月-31日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $436万
-$25,923/呎
+$26,078/呎
 (26年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $606万
-$25,145/呎
+$25,356/呎
 (26年-03月-11日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $590万
-$24,176/呎
+$24,376/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -6727,33 +6727,33 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $506万
-$25,842/呎
+$26,108/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $399万
-$23,738/呎
+$23,880/呎
 (24年-10月-16日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $600万
-$24,905/呎
+$25,113/呎
 (26年-03月-17日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $596万
-$24,422/呎
+$24,624/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -6767,33 +6767,33 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $501万
-$25,566/呎
+$25,830/呎
 (26年-04月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $427万
-$25,411/呎
+$25,563/呎
 (26年-02月-02日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $594万
-$24,660/呎
+$24,866/呎
 (26年-04月-20日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $602万
-$24,660/呎
+$24,864/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -6807,33 +6807,33 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $478万
-$24,362/呎
+$24,613/呎
 (25年-12月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $410万
-$24,429/呎
+$24,575/呎
 (25年-12月-22日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $566万
-$23,481/呎
+$23,678/呎
 (25年-12月-19日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $573万
-$23,484/呎
+$23,678/呎
 (25年-06月-13日)</t>
         </is>
       </c>
@@ -6847,33 +6847,33 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $464万
-$23,653/呎
+$23,897/呎
 (24年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $419万
-$24,917/呎
+$25,066/呎
 (26年-02月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $560万
-$23,257/呎
+$23,452/呎
 (25年-12月-02日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $579万
-$23,725/呎
+$23,921/呎
 (26年-02月-09日)</t>
         </is>
       </c>
@@ -6887,33 +6887,33 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $461万
-$23,541/呎
+$23,784/呎
 (25年-08月-21日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $404万
-$24,071/呎
+$24,216/呎
 (25年-12月-19日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $580万
-$24,079/呎
+$24,280/呎
 (26年-02月-24日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $565万
-$23,148/呎
+$23,339/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -6927,33 +6927,33 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $473万
-$24,128/呎
+$24,376/呎
 (25年-12月-30日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $410万
-$24,429/呎
+$24,575/呎
 (26年-02月-02日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>C | 241呎 (开放式)
+          <t>C | 239呎 (开放式)
 $572万
-$23,734/呎
+$23,933/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>D | 244呎 (开放式)
+          <t>D | 242呎 (开放式)
 $557万
-$22,816/呎
+$23,004/呎
 (25年-07月-14日)</t>
         </is>
       </c>
@@ -6967,17 +6967,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 196呎 (开放式)
+          <t>A | 194呎 (开放式)
 $450万
-$22,980/呎
+$23,216/呎
 (25年-03月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 168呎 (开放式)
+          <t>B | 167呎 (开放式)
 $406万
-$24,185/呎
+$24,329/呎
 (26年-02月-06日)</t>
         </is>
       </c>
@@ -6991,9 +6991,9 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>D | 209呎 (开放式)
+          <t>D | 208呎 (开放式)
 $548万
-$26,196/呎
+$26,322/呎
 (24年-11月-19日)</t>
         </is>
       </c>
